--- a/app/Data/accumulation/Kashima_Accumulated.xlsx
+++ b/app/Data/accumulation/Kashima_Accumulated.xlsx
@@ -18441,7 +18441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X42"/>
+  <dimension ref="A1:X43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="9" customWidth="1" style="115" min="1" max="1"/>
@@ -20522,7 +20522,56 @@
         <v>37</v>
       </c>
     </row>
-    <row r="43" ht="18" customHeight="1" s="115"/>
+    <row r="43" ht="18" customHeight="1" s="115">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ソテー</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>David Johnson</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>2695</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L0570</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="n">
+        <v>2695</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>2695</v>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>2695</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2695</v>
+      </c>
+    </row>
     <row r="44" ht="18" customHeight="1" s="115"/>
     <row r="45" ht="18" customHeight="1" s="115"/>
     <row r="46" ht="18" customHeight="1" s="115"/>
@@ -23482,52 +23531,52 @@
       <c r="R40" s="45" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1" s="115">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
         <is>
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr">
+      <c r="B41" s="0" t="inlineStr"/>
+      <c r="C41" s="0" t="inlineStr">
         <is>
           <t>郡山桑野食堂</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="0" t="inlineStr">
         <is>
           <t>Eshwar Potnuru</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="n">
+      <c r="E41" s="0" t="inlineStr"/>
+      <c r="F41" s="0" t="n">
         <v>2848</v>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
+      <c r="G41" s="0" t="inlineStr"/>
+      <c r="H41" s="0" t="inlineStr">
         <is>
           <t>T7380001003643</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="n">
+      <c r="I41" s="0" t="inlineStr"/>
+      <c r="J41" s="0" t="inlineStr"/>
+      <c r="K41" s="0" t="n">
         <v>24</v>
       </c>
-      <c r="L41" t="n">
+      <c r="L41" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="n">
+      <c r="M41" s="0" t="inlineStr"/>
+      <c r="N41" s="0" t="n">
         <v>2848</v>
       </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="n">
+      <c r="O41" s="0" t="inlineStr"/>
+      <c r="P41" s="0" t="n">
         <v>24</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="Q41" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="R41" t="n">
+      <c r="R41" s="0" t="n">
         <v>24</v>
       </c>
     </row>
